--- a/data/trans_orig/IP07KS_C10_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C10_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de poder prestar atención en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de poder prestar atención, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,64 +833,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35612</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26037</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43420</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20890</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5621</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39395</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37248</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26875</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45768</t>
+          <t>26327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>58138</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28871</t>
+          <t>45098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80572</t>
+          <t>66432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
+          <t>61,13%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>48,56%</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13076</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6567</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24609</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>37807</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16917</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>55100</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>61,12%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27287</t>
+          <t>20785</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>52419</t>
+          <t>27150</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84330</t>
+          <t>39092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9282</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5986</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9573</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6168</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13749</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,58%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10613</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7087</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14489</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>50,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,43%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21276</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27036</t>
+          <t>24946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9907</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6224</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13408</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>7837</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4454</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11727</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>37,55%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>56,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23977</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1585</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7084</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2418</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5211</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>24,97%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,74 +2766,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15117</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9365</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>86,73%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>53,73%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1619</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>61,11%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>62,92%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>17414</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>10745</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>88,17%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -2841,27 +2841,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19033</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2879,47 +2879,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2314</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8047</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>46,17%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2516</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38,89%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10440</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6940</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>13696</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>51,47%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>67,52%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>8636</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>5414</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>10977</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>58,76%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>36,84%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>74,68%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>19482</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>23565</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>65,72%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>9274</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>5941</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>12513</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>45,72%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>29,29%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>61,69%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>6062</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>9284</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>41,24%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>25,32%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>63,16%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -3674,82 +3674,82 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>571</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>571</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>9003</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>12305</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>46,28%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>27,06%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>5635</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>2961</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>9092</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>30,58%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>16,07%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>49,35%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20447</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>4137</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>11780</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>38,67%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>21,27%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>60,56%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>11106</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>7301</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>13931</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>60,28%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>39,63%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>75,61%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>14022</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>23821</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,37%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>7882</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>40,52%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>1684</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>4157</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -4582,82 +4582,82 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>3377</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>16,13%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>574</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>22224</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>15124</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>29260</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>47,63%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>32,41%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>62,71%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>20084</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>15151</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>23322</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>73,58%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>55,51%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>21763</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>28260</t>
+          <t>24616</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>43424</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>33902</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>49717</t>
+          <t>52031</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>13726</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>7844</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>22641</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>29,42%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>48,52%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>7211</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>3973</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>12144</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>44,49%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,22 +5000,22 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>30926</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -5038,107 +5038,107 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>9587</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>4936</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>16010</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16212</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -5151,82 +5151,82 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>904</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>4195</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>904</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>46661</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>46661</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>46661</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>45279</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>45279</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>45279</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>72574</t>
+          <t>75504</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>72574</t>
+          <t>75504</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>72574</t>
+          <t>75504</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>36713</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>28852</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>45793</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>42,08%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>33,07%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>52,49%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>29814</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>37758</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>46,95%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>59,46%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>34066</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>42956</t>
+          <t>39900</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>63880</t>
+          <t>69361</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>53941</t>
+          <t>57344</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>75437</t>
+          <t>80821</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>46853</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>37985</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>54767</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>53,7%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>43,54%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>62,77%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>32977</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>25388</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>39190</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>61,71%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>43842</t>
+          <t>36924</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>35140</t>
+          <t>29941</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>45106</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>76819</t>
+          <t>83777</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>71656</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>86837</t>
+          <t>95605</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>7949</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>822</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>886</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -5833,82 +5833,82 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>4761</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>938</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>138682</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>120430</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>157011</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>97293</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>61452</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>117701</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>46,23%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>140937</t>
+          <t>102223</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>121030</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>161428</t>
+          <t>115935</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>238229</t>
+          <t>240905</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>196708</t>
+          <t>219774</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>264467</t>
+          <t>264584</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>103328</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>85591</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>121521</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>38,38%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>45,14%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>105205</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>84149</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>144460</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>68,64%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>102614</t>
+          <t>86957</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>74334</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>121684</t>
+          <t>99397</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>207819</t>
+          <t>190285</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>182097</t>
+          <t>167962</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>256062</t>
+          <t>212585</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>23123</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>15647</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>34059</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>6820</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>3287</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>12548</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>23583</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>34377</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>41381</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>11730</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>6629</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6628,82 +6628,82 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>574</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>271285</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
